--- a/services_forms/035_house_painting_estimate_form--services_forms.xlsx
+++ b/services_forms/035_house_painting_estimate_form--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>house_painting_estimate_form_first_page</t>
+          <t>intro_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Page</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,23 +538,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>house_painting_estimate_form_first_page_2</t>
+          <t>house_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Second Page</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>House Type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select your house type</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,107 +570,127 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>first_page_first_field</t>
+          <t>painting_area</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>House Type</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Painting Area</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>List the areas to be painted</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_page_first_field_2</t>
+          <t>color_scheme</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Painting Area</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Color Scheme</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select your color scheme</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>first_page_first_field_3</t>
+          <t>stories</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Color Scheme</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Number of Stories</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select the number of stories</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_page_first_field_4</t>
+          <t>rooms</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Number of Stories</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Number of Rooms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Count the number of rooms</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>first_page_first_field_5</t>
+          <t>special_requests</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Room Count</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Special Requests</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Add any special notes</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,23 +700,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_page_last_field</t>
+          <t>painting_service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Special Requests</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Painting Service</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Do you need painting service?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +732,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>second_page_first_field</t>
+          <t>paint_color</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Painting Service</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Paint Color</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select your paint color</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,41 +759,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>second_page_first_field_2</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Paint Type</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Payment Method</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select your payment method</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>second_page_first_field_3</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paint Color</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Confirm the details</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,317 +813,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>second_page_last_field</t>
+          <t>total_cost</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Special Requests</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter the total cost</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>house_painting_estimate_form_last_page</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Last Page</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>house_painting_estimate_form_last_page_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Last Page 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>last_page_first_field</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Total Cost</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>last_page_first_field_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Payment Method</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>last_page_last_field</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Confirm</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>first_page_last_field</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>first_page_last_field_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>last_page_last_field_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>last_page_last_field_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>last_page_last_field_4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>last_page_last_field_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>last_page_last_field_6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>last_page_last_field_7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +843,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,245 +871,245 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_page_first_field_choices</t>
+          <t>house_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>single-family_home</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Single-family home</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_page_first_field_choices</t>
+          <t>house_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>first_page_first_field_2_choices</t>
+          <t>house_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>first_page_first_field_2_choices</t>
+          <t>house_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>first_page_first_field_3_choices</t>
+          <t>painting_area_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>living_room</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>first_page_first_field_3_choices</t>
+          <t>painting_area_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>first_page_first_field_4_choices</t>
+          <t>painting_area_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dining_room</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dining room</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>first_page_first_field_4_choices</t>
+          <t>painting_area_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bedroom_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bedroom 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>first_page_first_field_5_choices</t>
+          <t>painting_area_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>bedroom_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Bedroom 2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>first_page_first_field_5_choices</t>
+          <t>painting_area_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>second_page_first_field_choices</t>
+          <t>color_scheme_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>primary_color_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Primary color 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>second_page_first_field_choices</t>
+          <t>color_scheme_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>secondary_color_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Secondary color 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>second_page_first_field_2_choices</t>
+          <t>color_scheme_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>accent_color_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Accent color 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>second_page_first_field_2_choices</t>
+          <t>color_scheme_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>last_page_first_field_2_choices</t>
+          <t>stories_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1126,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>last_page_first_field_2_choices</t>
+          <t>stories_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,34 +1143,204 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>last_page_last_field_choices</t>
+          <t>stories_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>last_page_last_field_choices</t>
+          <t>painting_service_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>painting_service_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>paint_color_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>paint_color_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>paint_color_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>paint_color_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>payment_method_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>payment_method_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>credit_card</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Credit card</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>payment_method_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>confirm_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>confirm_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
